--- a/data/trans_bre/P1403-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P1403-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13,89</t>
+          <t>13,66</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>38,49%</t>
+          <t>39,02%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,92; 11,43</t>
+          <t>3,57; 11,33</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,23; 11,48</t>
+          <t>3,09; 11,45</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,03; 12,08</t>
+          <t>3,29; 12,57</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8,47; 18,51</t>
+          <t>8,7; 18,14</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>13,27; 47,01</t>
+          <t>12,69; 46,7</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,45; 35,29</t>
+          <t>8,12; 34,99</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,95; 42,41</t>
+          <t>9,61; 44,3</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>21,34; 56,12</t>
+          <t>22,39; 56,56</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6,82</t>
+          <t>-2,08</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>48,13%</t>
+          <t>-13,28%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 1,35</t>
+          <t>-2,1; 1,4</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,56; 0,43</t>
+          <t>-3,32; 0,61</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 2,19</t>
+          <t>-2,14; 2,06</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 26,66</t>
+          <t>-3,94; -0,25</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-28,05; 21,66</t>
+          <t>-26,75; 23,14</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-32,09; 5,07</t>
+          <t>-31,04; 7,18</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-17,6; 21,62</t>
+          <t>-17,6; 20,61</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-15,05; 208,19</t>
+          <t>-23,02; -1,71</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-6,01</t>
+          <t>-5,57</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-34,98%</t>
+          <t>-32,38%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,4; 1,73</t>
+          <t>-4,26; 1,93</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,24; 1,66</t>
+          <t>-5,99; 1,78</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,84; -0,92</t>
+          <t>-7,81; -0,82</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-9,14; -2,59</t>
+          <t>-8,87; -2,18</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-50,82; 32,18</t>
+          <t>-50,24; 34,22</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-54,67; 25,14</t>
+          <t>-55,12; 24,77</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-64,13; -8,18</t>
+          <t>-65,99; -7,53</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-48,4; -17,91</t>
+          <t>-46,42; -14,39</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7,19</t>
+          <t>1,78</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>39,97%</t>
+          <t>9,26%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,28; 5,75</t>
+          <t>2,31; 5,72</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,14; 6,0</t>
+          <t>2,28; 6,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,7; 4,42</t>
+          <t>0,75; 4,36</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,59; 22,32</t>
+          <t>0,12; 3,36</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>16,76; 48,07</t>
+          <t>16,24; 47,11</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,66; 37,68</t>
+          <t>12,58; 37,64</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,48; 30,87</t>
+          <t>4,62; 30,25</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8,17; 121,09</t>
+          <t>0,61; 18,41</t>
         </is>
       </c>
     </row>
